--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,6 +1510,208 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126421045</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Valsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555306</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973493</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126421043</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Valsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555306</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6973496</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -1515,7 +1515,7 @@
         <v>126421045</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>126421043</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>126421043</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>126421043</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>126421043</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 13486-2025 artfynd.xlsx
+++ b/artfynd/A 13486-2025 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>126421043</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
